--- a/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/03_外设接口资源表.xlsx
+++ b/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/03_外设接口资源表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project_2026\Git_test\stm32f4_DMA_UART_ring_RTOS\RTT_elog_DMA_UART_ring_project\00_Doc\01_资源分配表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB353E1B-D827-403D-9C33-21E6C1445622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,8 +25,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +34,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +71,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +373,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetFormatPr defaultRowHeight="20.149999999999999" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="2" customFormat="1" x14ac:dyDescent="0.5"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>